--- a/Datas/FriendShipData.xlsx
+++ b/Datas/FriendShipData.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="FriendShipData" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>

--- a/Datas/FriendShipData.xlsx
+++ b/Datas/FriendShipData.xlsx
@@ -38,35 +38,34 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>友好1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>友好2</t>
-  </si>
-  <si>
-    <t>友好3</t>
-  </si>
-  <si>
-    <t>友好4</t>
-  </si>
-  <si>
-    <t>友好5</t>
-  </si>
-  <si>
-    <t>友好6</t>
-  </si>
-  <si>
-    <t>友好7</t>
-  </si>
-  <si>
-    <t>友好8</t>
-  </si>
-  <si>
-    <t>友好9</t>
-  </si>
-  <si>
-    <t>友好10</t>
+    <t>初识</t>
+  </si>
+  <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>友善</t>
+  </si>
+  <si>
+    <t>熟悉</t>
+  </si>
+  <si>
+    <t>信赖</t>
+  </si>
+  <si>
+    <t>默契</t>
+  </si>
+  <si>
+    <t>亲近</t>
+  </si>
+  <si>
+    <t>深厚</t>
+  </si>
+  <si>
+    <t>挚友</t>
+  </si>
+  <si>
+    <t>知交</t>
   </si>
 </sst>
 </file>

--- a/Datas/FriendShipData.xlsx
+++ b/Datas/FriendShipData.xlsx
@@ -426,7 +426,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -437,7 +437,7 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -448,7 +448,7 @@
         <v>3</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -459,7 +459,7 @@
         <v>4</v>
       </c>
       <c r="C7">
-        <v>40</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -470,7 +470,7 @@
         <v>5</v>
       </c>
       <c r="C8">
-        <v>80</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -481,7 +481,7 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>160</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -492,7 +492,7 @@
         <v>7</v>
       </c>
       <c r="C10">
-        <v>320</v>
+        <v>640</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -503,7 +503,7 @@
         <v>8</v>
       </c>
       <c r="C11">
-        <v>640</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -514,7 +514,7 @@
         <v>9</v>
       </c>
       <c r="C12">
-        <v>1280</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="C13">
-        <v>2560</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
